--- a/resources/exports/skula-template.xlsx
+++ b/resources/exports/skula-template.xlsx
@@ -64,7 +64,7 @@
     <t>TROŠKOVI PRIJEVOZA</t>
   </si>
   <si>
-    <t>IZACI ZA NOĆENJE</t>
+    <t>IZDACI ZA NOĆENJE</t>
   </si>
   <si>
     <t>OSTALI TROŠKOVI</t>
